--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(5).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(5).xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="385">
   <si>
     <t>ID</t>
   </si>
@@ -96,122 +96,19 @@
     <t>综合考虑各种因素后，你打算如何回应同伴的问询？</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=1</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>choice(如实相告且大胆怀疑|jump(7))&amp;choice(简单提及但不屑一顾|jump(6))</t>
-  </si>
-  <si>
-    <t>源类型=type:selectBC; 层级=2</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=3</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>针筒、仪器、还有那些围在一起的白大褂，你将自己在幻觉中看到的一切简短而详实地告知了你此刻唯一能够信任的同伴，期待着两颗脑袋窦在一起能凑出一幅更加完整的拼图。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=4; 选项/备注=种种巧合连在一起即是真相</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>短短六十秒内，大卫赤色瞳孔里的情绪就像坐过山车一样经历数轮转变。从最初的困惑到中途的凝重，最终染上了一层细思极恐的暗红。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=5</t>
-  </si>
-  <si>
-    <t>71</t>
-  </si>
-  <si>
-    <t>大卫</t>
-  </si>
-  <si>
-    <t>所以，你的意思是，除了履历上的内容外，你小子还在这破地方接受过精神改造？</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_David; 层级=6</t>
-  </si>
-  <si>
-    <t>72</t>
-  </si>
-  <si>
-    <t>他故意摆出了一副轻松幽默的口吻，好像这样就能压制心中的震惊。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=7</t>
-  </si>
-  <si>
-    <t>73</t>
-  </si>
-  <si>
-    <t>你</t>
-  </si>
-  <si>
-    <t>不是我，而是我们。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=8</t>
-  </si>
-  <si>
-    <t>74</t>
-  </si>
-  <si>
-    <t>那些医生提到的实验者不止我一个，虽然没有明确说出你们的名字，但从丢失记忆的共性这一点来看......如果刚好又把我们三个派来执行这次任务，这未免有些太过巧合了吧。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=9</t>
-  </si>
-  <si>
-    <t>75</t>
-  </si>
-  <si>
-    <t>你尽力让自己的语气显得平静，仿佛探讨的话题与自己无关。但语气中些微的颤抖还是出卖了这份故作姿态的冷静。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=10</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>我知道这听起来很离谱，可姐姐的记者证就是在床下找到的，这种私人物品原本不可能出现在这里，但如果是我......在过去的某个时间点，自己遗留于此处，只有这样才解释的了为什么会出现一模一样的附件。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=11</t>
-  </si>
-  <si>
-    <t>77</t>
-  </si>
-  <si>
-    <t>你缓缓举起手中完全相同的两张证件，它们此刻仿佛穿着同一根电线的两端，一端接在此刻，一头埋于过去。将你的灵魂同这家污秽不堪的医院，用设备里的电流死死绑定在了一起。</t>
-  </si>
-  <si>
-    <t>bgfade(sntzm_david313-315(3)_64,1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=12</t>
-  </si>
-  <si>
-    <t>78</t>
-  </si>
-  <si>
-    <t>他听完你的话沉默了好一会儿，刚才刻意绷着的笑意彻底消失，眉头在脸上拧成了一个死结。这一切太过荒唐，又来得过于突然，换作任何人都不可能立刻消化得下这样的信息。</t>
+    <t>loadScript(sntzm_david313-315(6), 2)</t>
   </si>
   <si>
     <r>
-      <t>loadScript(</t>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
     </r>
     <r>
       <rPr>
@@ -219,7 +116,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>sntzm_david313-315(6)</t>
+      <t>层级</t>
     </r>
     <r>
       <rPr>
@@ -227,16 +124,10 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t>, 1)</t>
+      <t>=1</t>
     </r>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=13; gotomainline=大卫线313-315（最终分支）_1</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -264,6 +155,9 @@
     <t>9</t>
   </si>
   <si>
+    <t>你</t>
+  </si>
+  <si>
     <t>是你抓走了克拉克？两个房间里有关我们的私人物品也是你留下的杰作吧。</t>
   </si>
   <si>
@@ -285,6 +179,9 @@
     <t>男人的声音不急不慢，像是在炫耀自己的犯罪成果。</t>
   </si>
   <si>
+    <t>源类型=type:txt_pb; 层级=5</t>
+  </si>
+  <si>
     <t>12</t>
   </si>
   <si>
@@ -300,6 +197,9 @@
     <t>只听一记响指在扬声器中“咔”地炸开，克拉克稍显虚弱的声线随后而至，麻木的恍惚感将他的声音泡得发胀，每个字都带着刚从麻药里捞出来的迟钝。</t>
   </si>
   <si>
+    <t>源类型=type:txt_pb; 层级=7</t>
+  </si>
+  <si>
     <t>14</t>
   </si>
   <si>
@@ -324,6 +224,9 @@
     <t>16</t>
   </si>
   <si>
+    <t>大卫</t>
+  </si>
+  <si>
     <t>David_bandage</t>
   </si>
   <si>
@@ -354,6 +257,9 @@
     <t>这种愚蠢的天真，令对方既兴奋又鄙夷。</t>
   </si>
   <si>
+    <t>源类型=type:txt_pb; 层级=12</t>
+  </si>
+  <si>
     <t>19</t>
   </si>
   <si>
@@ -799,6 +705,9 @@
   </si>
   <si>
     <t>输出节点数</t>
+  </si>
+  <si>
+    <t>78</t>
   </si>
   <si>
     <t>选项节点数</t>
@@ -1354,6 +1263,11 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1506,11 +1420,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1819,31 +1728,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1852,115 +1758,118 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1971,7 +1880,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2507,7 +2416,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L79"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2628,18 +2537,18 @@
         <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" ht="45" spans="1:12">
+      <c r="L3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" ht="27" spans="1:12">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
@@ -2654,7 +2563,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H4" t="s">
         <v>15</v>
@@ -2666,15 +2575,15 @@
         <v>15</v>
       </c>
       <c r="K4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" ht="54" spans="1:12">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2692,7 +2601,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -2707,15 +2616,15 @@
         <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" ht="54" spans="1:12">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" ht="27" spans="1:12">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
@@ -2730,7 +2639,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -2745,15 +2654,15 @@
         <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" ht="40.5" spans="1:12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" ht="54" spans="1:12">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
@@ -2768,7 +2677,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -2783,15 +2692,15 @@
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" ht="27" spans="1:12">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
@@ -2806,7 +2715,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -2821,54 +2730,54 @@
         <v>15</v>
       </c>
       <c r="L8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:12">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" ht="42" spans="1:12">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" t="s">
-        <v>40</v>
-      </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
@@ -2882,7 +2791,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -2897,15 +2806,15 @@
         <v>15</v>
       </c>
       <c r="L10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" ht="55.5" spans="1:12">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
@@ -2920,7 +2829,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -2935,12 +2844,12 @@
         <v>15</v>
       </c>
       <c r="L11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" ht="40.5" spans="1:12">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" ht="54" spans="1:12">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -2958,7 +2867,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -2973,21 +2882,21 @@
         <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" ht="69" spans="1:12">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" ht="40.5" spans="1:12">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -2996,7 +2905,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3008,15 +2917,15 @@
         <v>15</v>
       </c>
       <c r="K13" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="L13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" ht="54" spans="1:12">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" ht="40.5" spans="1:12">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3025,7 +2934,7 @@
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3034,7 +2943,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3046,15 +2955,15 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="L14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" ht="54" spans="1:12">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3072,7 +2981,7 @@
         <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -3083,58 +2992,58 @@
       <c r="J15" t="s">
         <v>15</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>58</v>
+      <c r="K15" t="s">
+        <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" ht="54" spans="1:12">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>67</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" ht="54" spans="1:12">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
         <v>13</v>
       </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" t="s">
-        <v>15</v>
-      </c>
-      <c r="J16" t="s">
-        <v>15</v>
-      </c>
-      <c r="K16" t="s">
-        <v>15</v>
-      </c>
-      <c r="L16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" ht="27" spans="1:12">
-      <c r="A17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" t="s">
-        <v>62</v>
-      </c>
       <c r="C17" t="s">
         <v>14</v>
       </c>
@@ -3148,7 +3057,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3160,95 +3069,95 @@
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="L17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" ht="54" spans="1:12">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" ht="40.5" spans="1:12">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" t="s">
+        <v>15</v>
+      </c>
+      <c r="K18" t="s">
+        <v>15</v>
+      </c>
+      <c r="L18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" t="s">
+        <v>15</v>
+      </c>
+      <c r="L19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" ht="27" spans="1:12">
+      <c r="A20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" t="s">
         <v>13</v>
       </c>
-      <c r="C18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" t="s">
-        <v>67</v>
-      </c>
-      <c r="H18" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" t="s">
-        <v>15</v>
-      </c>
-      <c r="K18" t="s">
-        <v>15</v>
-      </c>
-      <c r="L18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" ht="27" spans="1:12">
-      <c r="A19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" t="s">
-        <v>70</v>
-      </c>
-      <c r="H19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" t="s">
-        <v>15</v>
-      </c>
-      <c r="K19" t="s">
-        <v>15</v>
-      </c>
-      <c r="L19" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="20" ht="54" spans="1:12">
-      <c r="A20" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" t="s">
-        <v>62</v>
-      </c>
       <c r="C20" t="s">
         <v>14</v>
       </c>
@@ -3262,7 +3171,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3277,15 +3186,15 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" ht="27" spans="1:12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" ht="57" spans="1:12">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
@@ -3300,7 +3209,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3315,15 +3224,15 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" ht="27" spans="1:12">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
@@ -3338,7 +3247,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3353,12 +3262,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" ht="42" spans="1:12">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3376,7 +3285,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3391,15 +3300,15 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" ht="27" spans="1:12">
       <c r="A24" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
@@ -3414,7 +3323,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3429,12 +3338,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" ht="54" spans="1:12">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" ht="40.5" spans="1:12">
       <c r="A25" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3452,7 +3361,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3467,21 +3376,21 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" ht="40.5" spans="1:12">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" ht="45" spans="1:12">
       <c r="A26" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="E26" t="s">
         <v>15</v>
@@ -3490,7 +3399,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3502,15 +3411,15 @@
         <v>15</v>
       </c>
       <c r="K26" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="27" ht="40.5" spans="1:12">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" ht="27" spans="1:12">
       <c r="A27" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3519,7 +3428,7 @@
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="E27" t="s">
         <v>15</v>
@@ -3528,7 +3437,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3540,15 +3449,15 @@
         <v>15</v>
       </c>
       <c r="K27" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" ht="45" spans="1:12">
       <c r="A28" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3566,7 +3475,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>99</v>
+        <v>15</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3578,18 +3487,18 @@
         <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>15</v>
+        <v>103</v>
       </c>
       <c r="L28" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" ht="54" spans="1:12">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
@@ -3604,7 +3513,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>101</v>
+        <v>15</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3619,12 +3528,12 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="30" ht="54" spans="1:12">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" ht="40.5" spans="1:12">
       <c r="A30" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3642,7 +3551,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3657,15 +3566,15 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="31" ht="40.5" spans="1:12">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
@@ -3680,7 +3589,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3695,15 +3604,15 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="32" ht="27" spans="1:12">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -3718,7 +3627,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3733,12 +3642,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" ht="27" spans="1:12">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="33" ht="40.5" spans="1:12">
       <c r="A33" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3756,7 +3665,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3771,21 +3680,21 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" ht="57" spans="1:12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" ht="30" spans="1:12">
       <c r="A34" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C34" t="s">
         <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="E34" t="s">
         <v>15</v>
@@ -3794,7 +3703,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3806,24 +3715,24 @@
         <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="L34" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" ht="40.5" spans="1:12">
       <c r="A35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -3832,7 +3741,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -3844,18 +3753,18 @@
         <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="L35" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="36" ht="42" spans="1:12">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="36" ht="27" spans="1:12">
       <c r="A36" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
@@ -3870,7 +3779,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -3885,15 +3794,15 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="37" ht="27" spans="1:12">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B37" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
@@ -3908,7 +3817,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -3923,12 +3832,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38" ht="40.5" spans="1:12">
       <c r="A38" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -3946,7 +3855,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -3961,15 +3870,15 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="39" ht="45" spans="1:12">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="39" ht="43.5" spans="1:12">
       <c r="A39" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B39" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
@@ -3984,7 +3893,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -3999,12 +3908,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="40" ht="27" spans="1:12">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" ht="40.5" spans="1:12">
       <c r="A40" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4022,7 +3931,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4037,12 +3946,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="41" ht="45" spans="1:12">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="41" ht="57" spans="1:12">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4060,7 +3969,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>15</v>
+        <v>141</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4072,18 +3981,18 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>137</v>
+        <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="42" ht="27" spans="1:12">
       <c r="A42" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
         <v>14</v>
@@ -4098,7 +4007,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>15</v>
+        <v>144</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4113,12 +4022,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="43" ht="40.5" spans="1:12">
       <c r="A43" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4136,7 +4045,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4151,15 +4060,15 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="C44" t="s">
         <v>14</v>
@@ -4174,7 +4083,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4189,15 +4098,15 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="45" ht="27" spans="1:12">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="45" ht="54" spans="1:12">
       <c r="A45" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="B45" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
@@ -4212,7 +4121,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4224,15 +4133,15 @@
         <v>15</v>
       </c>
       <c r="K45" t="s">
-        <v>15</v>
+        <v>154</v>
       </c>
       <c r="L45" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="46" ht="40.5" spans="1:12">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="46" ht="54" spans="1:12">
       <c r="A46" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4250,7 +4159,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4265,21 +4174,21 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="47" ht="30" spans="1:12">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B47" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4288,7 +4197,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>154</v>
+        <v>15</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4300,24 +4209,24 @@
         <v>15</v>
       </c>
       <c r="K47" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>155</v>
+        <v>106</v>
       </c>
     </row>
     <row r="48" ht="40.5" spans="1:12">
       <c r="A48" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B48" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4326,7 +4235,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4338,18 +4247,18 @@
         <v>15</v>
       </c>
       <c r="K48" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="49" ht="27" spans="1:12">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
@@ -4364,7 +4273,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4379,15 +4288,15 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
@@ -4402,7 +4311,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4417,12 +4326,12 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="51" ht="40.5" spans="1:12">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="51" ht="55.5" spans="1:12">
       <c r="A51" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4440,7 +4349,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4455,15 +4364,15 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="52" ht="43.5" spans="1:12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="52" ht="27" spans="1:12">
       <c r="A52" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
@@ -4478,7 +4387,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4493,15 +4402,15 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="53" ht="40.5" spans="1:12">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>174</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
@@ -4516,7 +4425,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4531,12 +4440,12 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="54" ht="57" spans="1:12">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4554,7 +4463,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4569,92 +4478,92 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" ht="27" spans="1:12">
       <c r="A55" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B55" t="s">
+        <v>174</v>
+      </c>
+      <c r="C55" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s">
+        <v>180</v>
+      </c>
+      <c r="H55" t="s">
+        <v>15</v>
+      </c>
+      <c r="I55" t="s">
+        <v>15</v>
+      </c>
+      <c r="J55" t="s">
+        <v>15</v>
+      </c>
+      <c r="K55" t="s">
+        <v>15</v>
+      </c>
+      <c r="L55" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="56" ht="43.5" spans="1:12">
+      <c r="A56" t="s">
+        <v>182</v>
+      </c>
+      <c r="B56" t="s">
+        <v>174</v>
+      </c>
+      <c r="C56" t="s">
+        <v>14</v>
+      </c>
+      <c r="D56" t="s">
+        <v>15</v>
+      </c>
+      <c r="E56" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" t="s">
+        <v>183</v>
+      </c>
+      <c r="H56" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" t="s">
+        <v>15</v>
+      </c>
+      <c r="J56" t="s">
+        <v>15</v>
+      </c>
+      <c r="K56" t="s">
+        <v>15</v>
+      </c>
+      <c r="L56" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="57" ht="27" spans="1:12">
+      <c r="A57" t="s">
+        <v>185</v>
+      </c>
+      <c r="B57" t="s">
         <v>13</v>
       </c>
-      <c r="C55" t="s">
-        <v>14</v>
-      </c>
-      <c r="D55" t="s">
-        <v>15</v>
-      </c>
-      <c r="E55" t="s">
-        <v>15</v>
-      </c>
-      <c r="F55" t="s">
-        <v>15</v>
-      </c>
-      <c r="G55" t="s">
-        <v>178</v>
-      </c>
-      <c r="H55" t="s">
-        <v>15</v>
-      </c>
-      <c r="I55" t="s">
-        <v>15</v>
-      </c>
-      <c r="J55" t="s">
-        <v>15</v>
-      </c>
-      <c r="K55" t="s">
-        <v>15</v>
-      </c>
-      <c r="L55" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="56" ht="40.5" spans="1:12">
-      <c r="A56" t="s">
-        <v>180</v>
-      </c>
-      <c r="B56" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" t="s">
-        <v>14</v>
-      </c>
-      <c r="D56" t="s">
-        <v>15</v>
-      </c>
-      <c r="E56" t="s">
-        <v>15</v>
-      </c>
-      <c r="F56" t="s">
-        <v>15</v>
-      </c>
-      <c r="G56" t="s">
-        <v>181</v>
-      </c>
-      <c r="H56" t="s">
-        <v>15</v>
-      </c>
-      <c r="I56" t="s">
-        <v>15</v>
-      </c>
-      <c r="J56" t="s">
-        <v>15</v>
-      </c>
-      <c r="K56" t="s">
-        <v>15</v>
-      </c>
-      <c r="L56" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12">
-      <c r="A57" t="s">
-        <v>183</v>
-      </c>
-      <c r="B57" t="s">
-        <v>40</v>
-      </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
@@ -4668,7 +4577,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4683,12 +4592,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="58" ht="54" spans="1:12">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="58" ht="57" spans="1:12">
       <c r="A58" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4706,7 +4615,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>187</v>
+        <v>141</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4718,15 +4627,15 @@
         <v>15</v>
       </c>
       <c r="K58" t="s">
+        <v>15</v>
+      </c>
+      <c r="L58" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="59" ht="27" spans="1:12">
+      <c r="A59" t="s">
         <v>188</v>
-      </c>
-      <c r="L58" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="59" ht="54" spans="1:12">
-      <c r="A59" t="s">
-        <v>190</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4744,179 +4653,179 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
+        <v>144</v>
+      </c>
+      <c r="H59" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" t="s">
+        <v>15</v>
+      </c>
+      <c r="J59" t="s">
+        <v>15</v>
+      </c>
+      <c r="K59" t="s">
+        <v>15</v>
+      </c>
+      <c r="L59" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="60" ht="27" spans="1:12">
+      <c r="A60" t="s">
+        <v>189</v>
+      </c>
+      <c r="B60" t="s">
+        <v>54</v>
+      </c>
+      <c r="C60" t="s">
+        <v>14</v>
+      </c>
+      <c r="D60" t="s">
+        <v>15</v>
+      </c>
+      <c r="E60" t="s">
+        <v>15</v>
+      </c>
+      <c r="F60" t="s">
+        <v>15</v>
+      </c>
+      <c r="G60" t="s">
+        <v>190</v>
+      </c>
+      <c r="H60" t="s">
+        <v>15</v>
+      </c>
+      <c r="I60" t="s">
+        <v>15</v>
+      </c>
+      <c r="J60" t="s">
+        <v>15</v>
+      </c>
+      <c r="K60" t="s">
+        <v>15</v>
+      </c>
+      <c r="L60" t="s">
         <v>191</v>
       </c>
-      <c r="H59" t="s">
-        <v>15</v>
-      </c>
-      <c r="I59" t="s">
-        <v>15</v>
-      </c>
-      <c r="J59" t="s">
-        <v>15</v>
-      </c>
-      <c r="K59" t="s">
-        <v>15</v>
-      </c>
-      <c r="L59" t="s">
+    </row>
+    <row r="61" ht="27" spans="1:12">
+      <c r="A61" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="60" spans="1:12">
-      <c r="A60" t="s">
+      <c r="B61" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" t="s">
+        <v>15</v>
+      </c>
+      <c r="F61" t="s">
+        <v>15</v>
+      </c>
+      <c r="G61" t="s">
         <v>193</v>
       </c>
-      <c r="B60" t="s">
-        <v>40</v>
-      </c>
-      <c r="C60" t="s">
-        <v>14</v>
-      </c>
-      <c r="D60" t="s">
-        <v>15</v>
-      </c>
-      <c r="E60" t="s">
-        <v>15</v>
-      </c>
-      <c r="F60" t="s">
-        <v>15</v>
-      </c>
-      <c r="G60" t="s">
-        <v>15</v>
-      </c>
-      <c r="H60" t="s">
-        <v>15</v>
-      </c>
-      <c r="I60" t="s">
-        <v>15</v>
-      </c>
-      <c r="J60" t="s">
-        <v>15</v>
-      </c>
-      <c r="K60" t="s">
-        <v>15</v>
-      </c>
-      <c r="L60" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="61" ht="40.5" spans="1:12">
-      <c r="A61" t="s">
+      <c r="H61" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" t="s">
+        <v>15</v>
+      </c>
+      <c r="J61" t="s">
+        <v>15</v>
+      </c>
+      <c r="K61" t="s">
+        <v>15</v>
+      </c>
+      <c r="L61" t="s">
         <v>194</v>
       </c>
-      <c r="B61" t="s">
+    </row>
+    <row r="62" ht="40.5" spans="1:12">
+      <c r="A62" t="s">
+        <v>195</v>
+      </c>
+      <c r="B62" t="s">
         <v>13</v>
       </c>
-      <c r="C61" t="s">
-        <v>14</v>
-      </c>
-      <c r="D61" t="s">
-        <v>15</v>
-      </c>
-      <c r="E61" t="s">
-        <v>15</v>
-      </c>
-      <c r="F61" t="s">
-        <v>15</v>
-      </c>
-      <c r="G61" t="s">
-        <v>195</v>
-      </c>
-      <c r="H61" t="s">
-        <v>15</v>
-      </c>
-      <c r="I61" t="s">
-        <v>15</v>
-      </c>
-      <c r="J61" t="s">
-        <v>15</v>
-      </c>
-      <c r="K61" t="s">
-        <v>15</v>
-      </c>
-      <c r="L61" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12">
-      <c r="A62" t="s">
+      <c r="C62" t="s">
+        <v>14</v>
+      </c>
+      <c r="D62" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" t="s">
+        <v>15</v>
+      </c>
+      <c r="G62" t="s">
         <v>196</v>
       </c>
-      <c r="B62" t="s">
-        <v>62</v>
-      </c>
-      <c r="C62" t="s">
-        <v>14</v>
-      </c>
-      <c r="D62" t="s">
-        <v>15</v>
-      </c>
-      <c r="E62" t="s">
-        <v>15</v>
-      </c>
-      <c r="F62" t="s">
-        <v>15</v>
-      </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
+        <v>15</v>
+      </c>
+      <c r="I62" t="s">
+        <v>15</v>
+      </c>
+      <c r="J62" t="s">
+        <v>15</v>
+      </c>
+      <c r="K62" t="s">
+        <v>154</v>
+      </c>
+      <c r="L62" t="s">
         <v>197</v>
       </c>
-      <c r="H62" t="s">
-        <v>15</v>
-      </c>
-      <c r="I62" t="s">
-        <v>15</v>
-      </c>
-      <c r="J62" t="s">
-        <v>15</v>
-      </c>
-      <c r="K62" t="s">
-        <v>15</v>
-      </c>
-      <c r="L62" t="s">
+    </row>
+    <row r="63" ht="40.5" spans="1:12">
+      <c r="A63" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="63" spans="1:12">
-      <c r="A63" t="s">
+      <c r="B63" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" t="s">
+        <v>15</v>
+      </c>
+      <c r="F63" t="s">
+        <v>15</v>
+      </c>
+      <c r="G63" t="s">
         <v>199</v>
       </c>
-      <c r="B63" t="s">
-        <v>40</v>
-      </c>
-      <c r="C63" t="s">
-        <v>14</v>
-      </c>
-      <c r="D63" t="s">
-        <v>15</v>
-      </c>
-      <c r="E63" t="s">
-        <v>15</v>
-      </c>
-      <c r="F63" t="s">
-        <v>15</v>
-      </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
+        <v>15</v>
+      </c>
+      <c r="I63" t="s">
+        <v>15</v>
+      </c>
+      <c r="J63" t="s">
+        <v>15</v>
+      </c>
+      <c r="K63" t="s">
+        <v>15</v>
+      </c>
+      <c r="L63" t="s">
         <v>200</v>
       </c>
-      <c r="H63" t="s">
-        <v>15</v>
-      </c>
-      <c r="I63" t="s">
-        <v>15</v>
-      </c>
-      <c r="J63" t="s">
-        <v>15</v>
-      </c>
-      <c r="K63" t="s">
-        <v>15</v>
-      </c>
-      <c r="L63" t="s">
+    </row>
+    <row r="64" ht="40.5" spans="1:12">
+      <c r="A64" t="s">
         <v>201</v>
-      </c>
-    </row>
-    <row r="64" ht="55.5" spans="1:12">
-      <c r="A64" t="s">
-        <v>202</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -4934,27 +4843,27 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
+        <v>202</v>
+      </c>
+      <c r="H64" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" t="s">
+        <v>15</v>
+      </c>
+      <c r="J64" t="s">
+        <v>15</v>
+      </c>
+      <c r="K64" t="s">
+        <v>15</v>
+      </c>
+      <c r="L64" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12">
+      <c r="A65" t="s">
         <v>203</v>
-      </c>
-      <c r="H64" t="s">
-        <v>15</v>
-      </c>
-      <c r="I64" t="s">
-        <v>15</v>
-      </c>
-      <c r="J64" t="s">
-        <v>15</v>
-      </c>
-      <c r="K64" t="s">
-        <v>15</v>
-      </c>
-      <c r="L64" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="65" ht="27" spans="1:12">
-      <c r="A65" t="s">
-        <v>204</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -4972,554 +4881,60 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" t="s">
+        <v>15</v>
+      </c>
+      <c r="I65" t="s">
+        <v>15</v>
+      </c>
+      <c r="J65" t="s">
+        <v>15</v>
+      </c>
+      <c r="K65" t="s">
+        <v>15</v>
+      </c>
+      <c r="L65" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="66" ht="40.5" spans="1:12">
+      <c r="A66" t="s">
         <v>205</v>
       </c>
-      <c r="H65" t="s">
-        <v>15</v>
-      </c>
-      <c r="I65" t="s">
-        <v>15</v>
-      </c>
-      <c r="J65" t="s">
-        <v>15</v>
-      </c>
-      <c r="K65" t="s">
-        <v>15</v>
-      </c>
-      <c r="L65" t="s">
+      <c r="B66" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="66" spans="1:12">
-      <c r="A66" t="s">
+      <c r="H66" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" t="s">
+        <v>15</v>
+      </c>
+      <c r="J66" t="s">
+        <v>15</v>
+      </c>
+      <c r="K66" t="s">
+        <v>15</v>
+      </c>
+      <c r="L66" t="s">
         <v>207</v>
-      </c>
-      <c r="B66" t="s">
-        <v>208</v>
-      </c>
-      <c r="C66" t="s">
-        <v>14</v>
-      </c>
-      <c r="D66" t="s">
-        <v>15</v>
-      </c>
-      <c r="E66" t="s">
-        <v>15</v>
-      </c>
-      <c r="F66" t="s">
-        <v>15</v>
-      </c>
-      <c r="G66" t="s">
-        <v>209</v>
-      </c>
-      <c r="H66" t="s">
-        <v>15</v>
-      </c>
-      <c r="I66" t="s">
-        <v>15</v>
-      </c>
-      <c r="J66" t="s">
-        <v>15</v>
-      </c>
-      <c r="K66" t="s">
-        <v>15</v>
-      </c>
-      <c r="L66" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12">
-      <c r="A67" t="s">
-        <v>211</v>
-      </c>
-      <c r="B67" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" t="s">
-        <v>14</v>
-      </c>
-      <c r="D67" t="s">
-        <v>15</v>
-      </c>
-      <c r="E67" t="s">
-        <v>15</v>
-      </c>
-      <c r="F67" t="s">
-        <v>15</v>
-      </c>
-      <c r="G67" t="s">
-        <v>212</v>
-      </c>
-      <c r="H67" t="s">
-        <v>15</v>
-      </c>
-      <c r="I67" t="s">
-        <v>15</v>
-      </c>
-      <c r="J67" t="s">
-        <v>15</v>
-      </c>
-      <c r="K67" t="s">
-        <v>15</v>
-      </c>
-      <c r="L67" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="68" ht="27" spans="1:12">
-      <c r="A68" t="s">
-        <v>213</v>
-      </c>
-      <c r="B68" t="s">
-        <v>208</v>
-      </c>
-      <c r="C68" t="s">
-        <v>14</v>
-      </c>
-      <c r="D68" t="s">
-        <v>15</v>
-      </c>
-      <c r="E68" t="s">
-        <v>15</v>
-      </c>
-      <c r="F68" t="s">
-        <v>15</v>
-      </c>
-      <c r="G68" t="s">
-        <v>214</v>
-      </c>
-      <c r="H68" t="s">
-        <v>15</v>
-      </c>
-      <c r="I68" t="s">
-        <v>15</v>
-      </c>
-      <c r="J68" t="s">
-        <v>15</v>
-      </c>
-      <c r="K68" t="s">
-        <v>15</v>
-      </c>
-      <c r="L68" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="69" ht="43.5" spans="1:12">
-      <c r="A69" t="s">
-        <v>216</v>
-      </c>
-      <c r="B69" t="s">
-        <v>208</v>
-      </c>
-      <c r="C69" t="s">
-        <v>14</v>
-      </c>
-      <c r="D69" t="s">
-        <v>15</v>
-      </c>
-      <c r="E69" t="s">
-        <v>15</v>
-      </c>
-      <c r="F69" t="s">
-        <v>15</v>
-      </c>
-      <c r="G69" t="s">
-        <v>217</v>
-      </c>
-      <c r="H69" t="s">
-        <v>15</v>
-      </c>
-      <c r="I69" t="s">
-        <v>15</v>
-      </c>
-      <c r="J69" t="s">
-        <v>15</v>
-      </c>
-      <c r="K69" t="s">
-        <v>15</v>
-      </c>
-      <c r="L69" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="70" ht="27" spans="1:12">
-      <c r="A70" t="s">
-        <v>219</v>
-      </c>
-      <c r="B70" t="s">
-        <v>13</v>
-      </c>
-      <c r="C70" t="s">
-        <v>14</v>
-      </c>
-      <c r="D70" t="s">
-        <v>15</v>
-      </c>
-      <c r="E70" t="s">
-        <v>15</v>
-      </c>
-      <c r="F70" t="s">
-        <v>15</v>
-      </c>
-      <c r="G70" t="s">
-        <v>220</v>
-      </c>
-      <c r="H70" t="s">
-        <v>15</v>
-      </c>
-      <c r="I70" t="s">
-        <v>15</v>
-      </c>
-      <c r="J70" t="s">
-        <v>15</v>
-      </c>
-      <c r="K70" t="s">
-        <v>15</v>
-      </c>
-      <c r="L70" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="71" ht="57" spans="1:12">
-      <c r="A71" t="s">
-        <v>221</v>
-      </c>
-      <c r="B71" t="s">
-        <v>13</v>
-      </c>
-      <c r="C71" t="s">
-        <v>14</v>
-      </c>
-      <c r="D71" t="s">
-        <v>15</v>
-      </c>
-      <c r="E71" t="s">
-        <v>15</v>
-      </c>
-      <c r="F71" t="s">
-        <v>15</v>
-      </c>
-      <c r="G71" t="s">
-        <v>175</v>
-      </c>
-      <c r="H71" t="s">
-        <v>15</v>
-      </c>
-      <c r="I71" t="s">
-        <v>15</v>
-      </c>
-      <c r="J71" t="s">
-        <v>15</v>
-      </c>
-      <c r="K71" t="s">
-        <v>15</v>
-      </c>
-      <c r="L71" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="72" ht="27" spans="1:12">
-      <c r="A72" t="s">
-        <v>222</v>
-      </c>
-      <c r="B72" t="s">
-        <v>13</v>
-      </c>
-      <c r="C72" t="s">
-        <v>14</v>
-      </c>
-      <c r="D72" t="s">
-        <v>15</v>
-      </c>
-      <c r="E72" t="s">
-        <v>15</v>
-      </c>
-      <c r="F72" t="s">
-        <v>15</v>
-      </c>
-      <c r="G72" t="s">
-        <v>178</v>
-      </c>
-      <c r="H72" t="s">
-        <v>15</v>
-      </c>
-      <c r="I72" t="s">
-        <v>15</v>
-      </c>
-      <c r="J72" t="s">
-        <v>15</v>
-      </c>
-      <c r="K72" t="s">
-        <v>15</v>
-      </c>
-      <c r="L72" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="73" ht="27" spans="1:12">
-      <c r="A73" t="s">
-        <v>223</v>
-      </c>
-      <c r="B73" t="s">
-        <v>33</v>
-      </c>
-      <c r="C73" t="s">
-        <v>14</v>
-      </c>
-      <c r="D73" t="s">
-        <v>15</v>
-      </c>
-      <c r="E73" t="s">
-        <v>15</v>
-      </c>
-      <c r="F73" t="s">
-        <v>15</v>
-      </c>
-      <c r="G73" t="s">
-        <v>224</v>
-      </c>
-      <c r="H73" t="s">
-        <v>15</v>
-      </c>
-      <c r="I73" t="s">
-        <v>15</v>
-      </c>
-      <c r="J73" t="s">
-        <v>15</v>
-      </c>
-      <c r="K73" t="s">
-        <v>15</v>
-      </c>
-      <c r="L73" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="74" ht="27" spans="1:12">
-      <c r="A74" t="s">
-        <v>226</v>
-      </c>
-      <c r="B74" t="s">
-        <v>40</v>
-      </c>
-      <c r="C74" t="s">
-        <v>14</v>
-      </c>
-      <c r="D74" t="s">
-        <v>15</v>
-      </c>
-      <c r="E74" t="s">
-        <v>15</v>
-      </c>
-      <c r="F74" t="s">
-        <v>15</v>
-      </c>
-      <c r="G74" t="s">
-        <v>227</v>
-      </c>
-      <c r="H74" t="s">
-        <v>15</v>
-      </c>
-      <c r="I74" t="s">
-        <v>15</v>
-      </c>
-      <c r="J74" t="s">
-        <v>15</v>
-      </c>
-      <c r="K74" t="s">
-        <v>15</v>
-      </c>
-      <c r="L74" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="75" ht="40.5" spans="1:12">
-      <c r="A75" t="s">
-        <v>229</v>
-      </c>
-      <c r="B75" t="s">
-        <v>13</v>
-      </c>
-      <c r="C75" t="s">
-        <v>14</v>
-      </c>
-      <c r="D75" t="s">
-        <v>15</v>
-      </c>
-      <c r="E75" t="s">
-        <v>15</v>
-      </c>
-      <c r="F75" t="s">
-        <v>15</v>
-      </c>
-      <c r="G75" t="s">
-        <v>230</v>
-      </c>
-      <c r="H75" t="s">
-        <v>15</v>
-      </c>
-      <c r="I75" t="s">
-        <v>15</v>
-      </c>
-      <c r="J75" t="s">
-        <v>15</v>
-      </c>
-      <c r="K75" t="s">
-        <v>188</v>
-      </c>
-      <c r="L75" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="76" ht="40.5" spans="1:12">
-      <c r="A76" t="s">
-        <v>232</v>
-      </c>
-      <c r="B76" t="s">
-        <v>40</v>
-      </c>
-      <c r="C76" t="s">
-        <v>14</v>
-      </c>
-      <c r="D76" t="s">
-        <v>15</v>
-      </c>
-      <c r="E76" t="s">
-        <v>15</v>
-      </c>
-      <c r="F76" t="s">
-        <v>15</v>
-      </c>
-      <c r="G76" t="s">
-        <v>233</v>
-      </c>
-      <c r="H76" t="s">
-        <v>15</v>
-      </c>
-      <c r="I76" t="s">
-        <v>15</v>
-      </c>
-      <c r="J76" t="s">
-        <v>15</v>
-      </c>
-      <c r="K76" t="s">
-        <v>15</v>
-      </c>
-      <c r="L76" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="77" ht="40.5" spans="1:12">
-      <c r="A77" t="s">
-        <v>235</v>
-      </c>
-      <c r="B77" t="s">
-        <v>13</v>
-      </c>
-      <c r="C77" t="s">
-        <v>14</v>
-      </c>
-      <c r="D77" t="s">
-        <v>15</v>
-      </c>
-      <c r="E77" t="s">
-        <v>15</v>
-      </c>
-      <c r="F77" t="s">
-        <v>15</v>
-      </c>
-      <c r="G77" t="s">
-        <v>236</v>
-      </c>
-      <c r="H77" t="s">
-        <v>15</v>
-      </c>
-      <c r="I77" t="s">
-        <v>15</v>
-      </c>
-      <c r="J77" t="s">
-        <v>15</v>
-      </c>
-      <c r="K77" t="s">
-        <v>15</v>
-      </c>
-      <c r="L77" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12">
-      <c r="A78" t="s">
-        <v>237</v>
-      </c>
-      <c r="B78" t="s">
-        <v>13</v>
-      </c>
-      <c r="C78" t="s">
-        <v>14</v>
-      </c>
-      <c r="D78" t="s">
-        <v>15</v>
-      </c>
-      <c r="E78" t="s">
-        <v>15</v>
-      </c>
-      <c r="F78" t="s">
-        <v>15</v>
-      </c>
-      <c r="G78" t="s">
-        <v>15</v>
-      </c>
-      <c r="H78" t="s">
-        <v>15</v>
-      </c>
-      <c r="I78" t="s">
-        <v>15</v>
-      </c>
-      <c r="J78" t="s">
-        <v>15</v>
-      </c>
-      <c r="K78" t="s">
-        <v>15</v>
-      </c>
-      <c r="L78" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="79" ht="40.5" spans="1:12">
-      <c r="A79" t="s">
-        <v>239</v>
-      </c>
-      <c r="B79" t="s">
-        <v>13</v>
-      </c>
-      <c r="C79" t="s">
-        <v>14</v>
-      </c>
-      <c r="D79" t="s">
-        <v>15</v>
-      </c>
-      <c r="E79" t="s">
-        <v>15</v>
-      </c>
-      <c r="F79" t="s">
-        <v>15</v>
-      </c>
-      <c r="G79" t="s">
-        <v>240</v>
-      </c>
-      <c r="H79" t="s">
-        <v>15</v>
-      </c>
-      <c r="I79" t="s">
-        <v>15</v>
-      </c>
-      <c r="J79" t="s">
-        <v>15</v>
-      </c>
-      <c r="K79" t="s">
-        <v>15</v>
-      </c>
-      <c r="L79" t="s">
-        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -5540,39 +4955,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>210</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="B3" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>249</v>
+        <v>216</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
@@ -5580,7 +4995,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>250</v>
+        <v>217</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -5588,7 +5003,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5596,66 +5011,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="B8" t="s">
-        <v>133</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="B10" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="B11" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="B12" t="s">
-        <v>257</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="B13" t="s">
-        <v>258</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="B14" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="B15" t="s">
-        <v>260</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -5677,616 +5092,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>263</v>
+        <v>230</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>265</v>
+        <v>232</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>266</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="B2" t="s">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="C2" t="s">
-        <v>269</v>
+        <v>236</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>237</v>
       </c>
       <c r="E2" t="s">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="F2" t="s">
-        <v>272</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="B3" t="s">
-        <v>273</v>
+        <v>240</v>
       </c>
       <c r="C3" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
       <c r="D3" t="s">
-        <v>275</v>
+        <v>242</v>
       </c>
       <c r="E3" t="s">
-        <v>276</v>
+        <v>243</v>
       </c>
       <c r="F3" t="s">
-        <v>277</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="B4" t="s">
-        <v>278</v>
+        <v>245</v>
       </c>
       <c r="C4" t="s">
-        <v>279</v>
+        <v>246</v>
       </c>
       <c r="D4" t="s">
-        <v>280</v>
+        <v>247</v>
       </c>
       <c r="E4" t="s">
-        <v>281</v>
+        <v>248</v>
       </c>
       <c r="F4" t="s">
-        <v>282</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="B5" t="s">
-        <v>283</v>
+        <v>250</v>
       </c>
       <c r="C5" t="s">
-        <v>284</v>
+        <v>251</v>
       </c>
       <c r="D5" t="s">
-        <v>285</v>
+        <v>252</v>
       </c>
       <c r="E5" t="s">
-        <v>286</v>
+        <v>253</v>
       </c>
       <c r="F5" t="s">
-        <v>287</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="B6" t="s">
-        <v>288</v>
+        <v>255</v>
       </c>
       <c r="C6" t="s">
-        <v>289</v>
+        <v>256</v>
       </c>
       <c r="D6" t="s">
-        <v>290</v>
+        <v>257</v>
       </c>
       <c r="E6" t="s">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="F6" t="s">
-        <v>292</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>267</v>
+        <v>234</v>
       </c>
       <c r="B7" t="s">
-        <v>293</v>
+        <v>260</v>
       </c>
       <c r="C7" t="s">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="D7" t="s">
-        <v>295</v>
+        <v>262</v>
       </c>
       <c r="E7" t="s">
-        <v>296</v>
+        <v>263</v>
       </c>
       <c r="F7" t="s">
-        <v>297</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="B8" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="C8" t="s">
-        <v>300</v>
+        <v>267</v>
       </c>
       <c r="D8" t="s">
-        <v>301</v>
+        <v>268</v>
       </c>
       <c r="E8" t="s">
-        <v>302</v>
+        <v>269</v>
       </c>
       <c r="F8" t="s">
-        <v>303</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="B9" t="s">
-        <v>304</v>
+        <v>271</v>
       </c>
       <c r="C9" t="s">
-        <v>305</v>
+        <v>272</v>
       </c>
       <c r="D9" t="s">
-        <v>306</v>
+        <v>273</v>
       </c>
       <c r="E9" t="s">
-        <v>307</v>
+        <v>274</v>
       </c>
       <c r="F9" t="s">
-        <v>308</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="B10" t="s">
-        <v>310</v>
+        <v>277</v>
       </c>
       <c r="C10" t="s">
-        <v>311</v>
+        <v>278</v>
       </c>
       <c r="D10" t="s">
-        <v>312</v>
+        <v>279</v>
       </c>
       <c r="E10" t="s">
-        <v>313</v>
+        <v>280</v>
       </c>
       <c r="F10" t="s">
-        <v>314</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="B11" t="s">
-        <v>315</v>
+        <v>282</v>
       </c>
       <c r="C11" t="s">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="D11" t="s">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="E11" t="s">
-        <v>318</v>
+        <v>285</v>
       </c>
       <c r="F11" t="s">
-        <v>319</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="B12" t="s">
-        <v>320</v>
+        <v>287</v>
       </c>
       <c r="C12" t="s">
-        <v>321</v>
+        <v>288</v>
       </c>
       <c r="D12" t="s">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="E12" t="s">
-        <v>323</v>
+        <v>290</v>
       </c>
       <c r="F12" t="s">
-        <v>324</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="B13" t="s">
-        <v>325</v>
+        <v>292</v>
       </c>
       <c r="C13" t="s">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="D13" t="s">
-        <v>327</v>
+        <v>294</v>
       </c>
       <c r="E13" t="s">
-        <v>328</v>
+        <v>295</v>
       </c>
       <c r="F13" t="s">
-        <v>329</v>
+        <v>296</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="B14" t="s">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="C14" t="s">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="D14" t="s">
-        <v>332</v>
+        <v>299</v>
       </c>
       <c r="E14" t="s">
-        <v>333</v>
+        <v>300</v>
       </c>
       <c r="F14" t="s">
-        <v>334</v>
+        <v>301</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="B15" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="C15" t="s">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="D15" t="s">
-        <v>337</v>
+        <v>304</v>
       </c>
       <c r="E15" t="s">
-        <v>338</v>
+        <v>305</v>
       </c>
       <c r="F15" t="s">
-        <v>339</v>
+        <v>306</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
+        <v>276</v>
+      </c>
+      <c r="B16" t="s">
+        <v>307</v>
+      </c>
+      <c r="C16" t="s">
+        <v>308</v>
+      </c>
+      <c r="D16" t="s">
         <v>309</v>
       </c>
-      <c r="B16" t="s">
-        <v>340</v>
-      </c>
-      <c r="C16" t="s">
-        <v>341</v>
-      </c>
-      <c r="D16" t="s">
-        <v>342</v>
-      </c>
       <c r="E16" t="s">
-        <v>343</v>
+        <v>310</v>
       </c>
       <c r="F16" t="s">
-        <v>344</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="B17" t="s">
-        <v>345</v>
+        <v>312</v>
       </c>
       <c r="C17" t="s">
-        <v>346</v>
+        <v>313</v>
       </c>
       <c r="D17" t="s">
-        <v>347</v>
+        <v>314</v>
       </c>
       <c r="E17" t="s">
-        <v>348</v>
+        <v>315</v>
       </c>
       <c r="F17" t="s">
-        <v>349</v>
+        <v>316</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="B18" t="s">
-        <v>350</v>
+        <v>317</v>
       </c>
       <c r="C18" t="s">
-        <v>351</v>
+        <v>318</v>
       </c>
       <c r="D18" t="s">
-        <v>352</v>
+        <v>319</v>
       </c>
       <c r="E18" t="s">
-        <v>353</v>
+        <v>320</v>
       </c>
       <c r="F18" t="s">
-        <v>354</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="B19" t="s">
-        <v>355</v>
+        <v>322</v>
       </c>
       <c r="C19" t="s">
-        <v>356</v>
+        <v>323</v>
       </c>
       <c r="D19" t="s">
-        <v>357</v>
+        <v>324</v>
       </c>
       <c r="E19" t="s">
-        <v>358</v>
+        <v>325</v>
       </c>
       <c r="F19" t="s">
-        <v>359</v>
+        <v>326</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="B20" t="s">
-        <v>360</v>
+        <v>327</v>
       </c>
       <c r="C20" t="s">
-        <v>361</v>
+        <v>328</v>
       </c>
       <c r="D20" t="s">
-        <v>362</v>
+        <v>329</v>
       </c>
       <c r="E20" t="s">
-        <v>363</v>
+        <v>330</v>
       </c>
       <c r="F20" t="s">
-        <v>364</v>
+        <v>331</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="B21" t="s">
-        <v>365</v>
+        <v>332</v>
       </c>
       <c r="C21" t="s">
-        <v>366</v>
+        <v>333</v>
       </c>
       <c r="D21" t="s">
-        <v>367</v>
+        <v>334</v>
       </c>
       <c r="E21" t="s">
-        <v>368</v>
+        <v>335</v>
       </c>
       <c r="F21" t="s">
-        <v>369</v>
+        <v>336</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="B22" t="s">
-        <v>370</v>
+        <v>337</v>
       </c>
       <c r="C22" t="s">
-        <v>371</v>
+        <v>338</v>
       </c>
       <c r="D22" t="s">
-        <v>372</v>
+        <v>339</v>
       </c>
       <c r="E22" t="s">
-        <v>373</v>
+        <v>340</v>
       </c>
       <c r="F22" t="s">
-        <v>374</v>
+        <v>341</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="B23" t="s">
-        <v>375</v>
+        <v>342</v>
       </c>
       <c r="C23" t="s">
-        <v>376</v>
+        <v>343</v>
       </c>
       <c r="D23" t="s">
-        <v>377</v>
+        <v>344</v>
       </c>
       <c r="E23" t="s">
-        <v>378</v>
+        <v>345</v>
       </c>
       <c r="F23" t="s">
-        <v>379</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="B24" t="s">
-        <v>380</v>
+        <v>347</v>
       </c>
       <c r="C24" t="s">
-        <v>381</v>
+        <v>348</v>
       </c>
       <c r="D24" t="s">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c r="E24" t="s">
-        <v>382</v>
+        <v>349</v>
       </c>
       <c r="F24" t="s">
-        <v>383</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>384</v>
+        <v>351</v>
       </c>
       <c r="B25" t="s">
-        <v>385</v>
+        <v>352</v>
       </c>
       <c r="C25" t="s">
-        <v>386</v>
+        <v>353</v>
       </c>
       <c r="D25" t="s">
-        <v>387</v>
+        <v>354</v>
       </c>
       <c r="E25" t="s">
-        <v>388</v>
+        <v>355</v>
       </c>
       <c r="F25" t="s">
-        <v>389</v>
+        <v>356</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>384</v>
+        <v>351</v>
       </c>
       <c r="B26" t="s">
-        <v>390</v>
+        <v>357</v>
       </c>
       <c r="C26" t="s">
-        <v>391</v>
+        <v>358</v>
       </c>
       <c r="D26" t="s">
-        <v>392</v>
+        <v>359</v>
       </c>
       <c r="E26" t="s">
-        <v>393</v>
+        <v>360</v>
       </c>
       <c r="F26" t="s">
-        <v>394</v>
+        <v>361</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>384</v>
+        <v>351</v>
       </c>
       <c r="B27" t="s">
-        <v>395</v>
+        <v>362</v>
       </c>
       <c r="C27" t="s">
-        <v>396</v>
+        <v>363</v>
       </c>
       <c r="D27" t="s">
-        <v>397</v>
+        <v>364</v>
       </c>
       <c r="E27" t="s">
-        <v>398</v>
+        <v>365</v>
       </c>
       <c r="F27" t="s">
-        <v>399</v>
+        <v>366</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>384</v>
+        <v>351</v>
       </c>
       <c r="B28" t="s">
-        <v>400</v>
+        <v>367</v>
       </c>
       <c r="C28" t="s">
-        <v>401</v>
+        <v>368</v>
       </c>
       <c r="D28" t="s">
-        <v>397</v>
+        <v>364</v>
       </c>
       <c r="E28" t="s">
-        <v>402</v>
+        <v>369</v>
       </c>
       <c r="F28" t="s">
-        <v>403</v>
+        <v>370</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>384</v>
+        <v>351</v>
       </c>
       <c r="B29" t="s">
-        <v>404</v>
+        <v>371</v>
       </c>
       <c r="C29" t="s">
-        <v>405</v>
+        <v>372</v>
       </c>
       <c r="D29" t="s">
-        <v>406</v>
+        <v>373</v>
       </c>
       <c r="E29" t="s">
-        <v>407</v>
+        <v>374</v>
       </c>
       <c r="F29" t="s">
-        <v>408</v>
+        <v>375</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>384</v>
+        <v>351</v>
       </c>
       <c r="B30" t="s">
-        <v>409</v>
+        <v>376</v>
       </c>
       <c r="C30" t="s">
-        <v>410</v>
+        <v>377</v>
       </c>
       <c r="D30" t="s">
-        <v>411</v>
+        <v>378</v>
       </c>
       <c r="E30" t="s">
-        <v>412</v>
+        <v>379</v>
       </c>
       <c r="F30" t="s">
-        <v>413</v>
+        <v>380</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>414</v>
+        <v>381</v>
       </c>
       <c r="B31" t="s">
-        <v>415</v>
+        <v>382</v>
       </c>
       <c r="C31" t="s">
-        <v>416</v>
+        <v>383</v>
       </c>
       <c r="D31" t="s">
-        <v>417</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(5).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_david313-315(5).xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="394">
   <si>
     <t>ID</t>
   </si>
@@ -99,8 +99,430 @@
     <t>loadScript(sntzm_david313-315(6), 2)</t>
   </si>
   <si>
+    <t>源类型=type:txt_pb; 层级=1; gotomainline=大卫线313-315（最终分支）_2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>？？？</t>
+  </si>
+  <si>
+    <t>令人感动的兄弟情谊，格莱特探员，没想到你真的会为了营救同伴而放弃探究自己的过去。</t>
+  </si>
+  <si>
+    <t>bgfade(sntzm_david313-315(5)_3,1)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Un; 层级=1</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>近乎张狂的喜悦在男人的字句间流动着，将你们本就所剩无几的安全感再一次榨干至极限。那些关于幕后黑手的猜测不再是自我惊吓的天方夜谭，明目张胆的暴露也恰恰说明了一切尽在对方掌握。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=2</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>你</t>
+  </si>
+  <si>
+    <t>是你抓走了克拉克？两个房间里有关我们的私人物品也是你留下的杰作吧。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=3</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>一部分，亚当。我并没有改变既有过去的能力，对于你所看到的，所见即所得。无论是大卫的录音，还是你姐姐的证件。我只是稍稍复原了一下房间里原有的布置。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Un; 层级=4</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>男人的声音不急不慢，像是在炫耀自己的犯罪成果。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=5</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>至于你们的朋友，既然你特地问了，若是不让他和你们打声招呼，未免就有些太过失礼了。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Un; 层级=6</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>只听一记响指在扬声器中“咔”地炸开，克拉克稍显虚弱的声线随后而至，麻木的恍惚感将他的声音泡得发胀，每个字都带着刚从麻药里捞出来的迟钝。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=7</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>克拉克</t>
+  </si>
+  <si>
+    <t>我这是......在哪里？</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Clark; 层级=8</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>你听见金属镣铐碰撞的脆响顺着线路传过来，那是你身为探员最为熟悉不过的声音之一，只是它本该出现在罪犯手上，而不是反过来束缚你年轻的同伴。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=9</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>大卫</t>
+  </si>
+  <si>
+    <t>David_bandage</t>
+  </si>
+  <si>
+    <t>臭小子，你现在能看得清周围吗？或者能不能听到周围的什么声音？我们需要更多信息来定位你的位置。</t>
+  </si>
+  <si>
+    <t>charfadein(L,1)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_David; 层级=10</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>大卫丝毫不顾始作俑者就在身旁的威胁，直接跳过一切无意义的问候，试图通过音频中的蛛丝马迹快速锁定他的位置。</t>
+  </si>
+  <si>
+    <t>charfadeout(L,1)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=11</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>这种愚蠢的天真，令对方既兴奋又鄙夷。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=12</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>别再用这种磨蹭又低效的方式沟通了，梅森探员。你们的朋友才刚从麻醉药的效果中清醒过来，你们与其问他，还不如问我。或许我的答案比他更可靠呢？</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Un; 层级=13</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>别有用意的示好裹着藏不住的恶意穿透了音响的杂音，换来的却只有你们紧扣扳机的手指。玩够了猫捉老鼠的游戏后，任何一次探出爪子的嘲弄，都只会进一步激起猎人的愤怒。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=14</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>你的回答将决定我们是否需要带你回去受审，或是把你永远留在这里，我们没空陪你玩什么猜谜游戏。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=15</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>呵......</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Un; 层级=16</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>他似乎听到什么笑话似得，不怀好意地低笑了两声。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=17</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>猜谜？那你可真是误会我了，亚当，而且误会得很深.......向你们撒谎，对你们隐瞒一切的另有其人，相反......我一直在试着把本该摆在你们面前的真相原原本本交还给你们。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Un; 层级=18</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>别听他乱说......</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Clark; 层级=19</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>被束缚的FBI似乎想要说些什么，但话音未落便被什么东西捂住了嘴，布料摩擦的窸窣过后，扬声器重新被那个带着笑意的声音填满。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=20</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>好了，克拉克。我只是让你出来打个招呼，别给自己加戏。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Un; 层级=21</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>没等大卫的下一句粗口伴随着对同伴的担忧一同喷入音响，神秘人口中的一串数字便瞬间压过了他的嗓门。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=22</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>B-512，海尔特探员就在这里。你们有一刻钟的时间来决定最后见到的是活着的他还是一具......嗯，FBI的尸体。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Un; 层级=23</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>对方的广播即将这句话的结束而切断，但或许你还来得及问出最后一个问题，你想问什么？</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=24</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>choice(我们有什么理由相信这不是另一个陷阱”|jump(32))&amp;choice(你就是亚波伦，对吧？|jump(33))</t>
+  </si>
+  <si>
+    <t>源类型=type:selectBC; 层级=25</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>jump(34)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=26</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>即将切断的通讯似乎因为这句话额外停留了几秒，像是正打算收工的渔夫又在水底钓起什么似的，为此多续上了一条蠕动的肥饵。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=27</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>对于随时都能除掉的死人，我没有撒谎的必要。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=28</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>否则我可以再多丢出几只和阿兰一样的怪物，而不是大费周章地请你们上楼做客。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=29</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>似乎对你的提问感到无趣，男人原本兴致勃勃的声线中掺入了一丝不加掩饰的厌恶。可还未等这份情绪发酵太久，又一个声音不合时宜地插了进来。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=30</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>是你把他变成那副模样的？把阿兰.斯科特。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_David; 层级=31</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>我只是给了他配了一副项圈而已，但将他驯成巴普洛夫的狗的，可是躲在你们想都想象不到的地方，坐享其成呢。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Un; 层级=32</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>至于是谁把他关进的这间驯狗屋，你难道不比任何人都更加清楚吗，梅森探员？</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=33</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>......！</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_David; 层级=34</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>随着舞台上最后一位演员的质问声被罪恶感卡在了喉咙，冲突和对峙的戏码转瞬间被滑稽的哑剧所取代，唯有闹剧的导演从容依旧。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=35</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>好了......你们已经为这些无聊的话题耽误了近2分钟的时间。也许是时候该想想怎么用剩下的13分钟，给海尔特探员谋一条活路了。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=36</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>嘈杂的电磁声在他声音断掉的瞬间陡然沉入黑暗，让病房中因承载太多过往而不堪重负的空气，再度回归虚无的死寂。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=37</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>“22点17分”，看着手机屏幕上跳动的荧光数字，迫切的焦虑很快浸润了你的每一根神经——克拉克还活着，而且位置已经暴露，这本是值得庆幸的消息。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=38</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>但倘若无法及时赶到，或是对方提前撕票，这种得而复失的痛苦将远比未知的煎熬更加难以承受。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=39</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>不等它急匆匆地跳到下一个数字，你的脚已经擅自朝门边移了过去，没有任何的解释或预兆，只因解救同伴本身就是一种无需商量的责任。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=40</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>走吧，克拉克还在等我们。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=41</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>浓稠的阴影在你眼角周围降下一圈暗沉的薄雾，仿佛还藏着什么尚未触及的秘密没有被发现。但现在，相较于分秒必争夺的营救，任何多余的停留都只会让克拉克的处境更加危险。</t>
+  </si>
+  <si>
+    <t>bgfade(sntzm_david313-315(5)_49,1)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=42</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>大卫的脚步紧随其后，因神秘人的那句话而产生的犹疑并没有影响他当下的判断。两束手电很快为了同一个目标齐刷刷地照向一处，在楼梯口的黑暗中撕开一条明亮的通路。</t>
+  </si>
+  <si>
     <r>
-      <t>源类型</t>
+      <t>loadScript(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>sntzm_david3F(1)</t>
     </r>
     <r>
       <rPr>
@@ -108,584 +530,181 @@
         <rFont val="Calibri"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">=type:txt_pb; </t>
+      <t>, 1)</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>层级</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>=1</t>
-    </r>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>？？？</t>
-  </si>
-  <si>
-    <t>令人感动的兄弟情谊，格莱特探员，没想到你真的会为了营救同伴而放弃探究自己的过去。</t>
-  </si>
-  <si>
-    <t>bgfade(sntzm_david313-315(5)_3,1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Un; 层级=1</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>近乎张狂的喜悦在男人的字句间流动着，将你们本就所剩无几的安全感再一次榨干至极限。那些关于幕后黑手的猜测不再是自我惊吓的天方夜谭，明目张胆的暴露也恰恰说明了一切尽在对方掌握。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=2</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>你</t>
-  </si>
-  <si>
-    <t>是你抓走了克拉克？两个房间里有关我们的私人物品也是你留下的杰作吧。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=3</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>一部分，亚当。我并没有改变既有过去的能力，对于你所看到的，所见即所得。无论是大卫的录音，还是你姐姐的证件。我只是稍稍复原了一下房间里原有的布置。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Un; 层级=4</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>男人的声音不急不慢，像是在炫耀自己的犯罪成果。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=5</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>至于你们的朋友，既然你特地问了，若是不让他和你们打声招呼，未免就有些太过失礼了。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Un; 层级=6</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>只听一记响指在扬声器中“咔”地炸开，克拉克稍显虚弱的声线随后而至，麻木的恍惚感将他的声音泡得发胀，每个字都带着刚从麻药里捞出来的迟钝。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=7</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>克拉克</t>
-  </si>
-  <si>
-    <t>我这是......在哪里？</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Clark; 层级=8</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>你听见金属镣铐碰撞的脆响顺着线路传过来，那是你身为探员最为熟悉不过的声音之一，只是它本该出现在罪犯手上，而不是反过来束缚你年轻的同伴。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=9</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>大卫</t>
-  </si>
-  <si>
-    <t>David_bandage</t>
-  </si>
-  <si>
-    <t>臭小子，你现在能看得清周围吗？或者能不能听到周围的什么声音？我们需要更多信息来定位你的位置。</t>
-  </si>
-  <si>
-    <t>charfadein(L,1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_David; 层级=10</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>大卫丝毫不顾始作俑者就在身旁的威胁，直接跳过一切无意义的问候，试图通过音频中的蛛丝马迹快速锁定他的位置。</t>
-  </si>
-  <si>
-    <t>charfadeout(L,1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=11</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>这种愚蠢的天真，令对方既兴奋又鄙夷。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=12</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>别再用这种磨蹭又低效的方式沟通了，梅森探员。你们的朋友才刚从麻醉药的效果中清醒过来，你们与其问他，还不如问我。或许我的答案比他更可靠呢？</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Un; 层级=13</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>别有用意的示好裹着藏不住的恶意穿透了音响的杂音，换来的却只有你们紧扣扳机的手指。玩够了猫捉老鼠的游戏后，任何一次探出爪子的嘲弄，都只会进一步激起猎人的愤怒。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=14</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>你的回答将决定我们是否需要带你回去受审，或是把你永远留在这里，我们没空陪你玩什么猜谜游戏。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=15</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>呵......</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Un; 层级=16</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>他似乎听到什么笑话似得，不怀好意地低笑了两声。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=17</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>猜谜？那你可真是误会我了，亚当，而且误会得很深.......向你们撒谎，对你们隐瞒一切的另有其人，相反......我一直在试着把本该摆在你们面前的真相原原本本交还给你们。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Un; 层级=18</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>别听他乱说......</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Clark; 层级=19</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>被束缚的FBI似乎想要说些什么，但话音未落便被什么东西捂住了嘴，布料摩擦的窸窣过后，扬声器重新被那个带着笑意的声音填满。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=20</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>好了，克拉克。我只是让你出来打个招呼，别给自己加戏。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Un; 层级=21</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>没等大卫的下一句粗口伴随着对同伴的担忧一同喷入音响，神秘人口中的一串数字便瞬间压过了他的嗓门。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=22</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>B-512，海尔特探员就在这里。你们有一刻钟的时间来决定最后见到的是活着的他还是一具......嗯，FBI的尸体。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Un; 层级=23</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>对方的广播即将这句话的结束而切断，但或许你还来得及问出最后一个问题，你想问什么？</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=24</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>choice(我们有什么理由相信这不是另一个陷阱”|jump(34))&amp;choice(你就是亚波伦，对吧？|jump(51))</t>
-  </si>
-  <si>
-    <t>源类型=type:selectBC; 层级=25</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=26</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>即将切断的通讯似乎因为这句话额外停留了几秒，像是正打算收工的渔夫又在水底钓起什么似的，为此多续上了一条蠕动的肥饵。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=27</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>对于随时都能除掉的死人，我没有撒谎的必要。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=28</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>否则我可以再多丢出几只和阿兰一样的怪物，而不是大费周章地请你们上楼做客。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=29</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>似乎对你的提问感到无趣，男人原本兴致勃勃的声线中掺入了一丝不加掩饰的厌恶。可还未等这份情绪发酵太久，又一个声音不合时宜地插了进来。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=30</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>是你把他变成那副模样的？把阿兰.斯科特。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_David; 层级=31</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>我只是给了他配了一副项圈而已，但将他驯成巴普洛夫的狗的，可是躲在你们想都想象不到的地方，坐享其成呢。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Un; 层级=32</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>至于是谁把他关进的这间驯狗屋，你难道不比任何人都更加清楚吗，梅森探员？</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=33</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>......！</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_David; 层级=34</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>随着舞台上最后一位演员的质问声被罪恶感卡在了喉咙，冲突和对峙的戏码转瞬间被滑稽的哑剧所取代，唯有闹剧的导演从容依旧。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=35</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>好了......你们已经为这些无聊的话题耽误了近2分钟的时间。也许是时候该想想怎么用剩下的13分钟，给海尔特探员谋一条活路了。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=36</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>嘈杂的电磁声在他声音断掉的瞬间陡然沉入黑暗，让病房中因承载太多过往而不堪重负的空气，再度回归虚无的死寂。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=37</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>“22点17分”，看着手机屏幕上跳动的荧光数字，迫切的焦虑很快浸润了你的每一根神经——克拉克还活着，而且位置已经暴露，这本是值得庆幸的消息。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=38</t>
-  </si>
-  <si>
-    <t>46</t>
-  </si>
-  <si>
-    <t>但倘若无法及时赶到，或是对方提前撕票，这种得而复失的痛苦将远比未知的煎熬更加难以承受。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=39</t>
-  </si>
-  <si>
-    <t>47</t>
-  </si>
-  <si>
-    <t>不等它急匆匆地跳到下一个数字，你的脚已经擅自朝门边移了过去，没有任何的解释或预兆，只因解救同伴本身就是一种无需商量的责任。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=40</t>
-  </si>
-  <si>
-    <t>48</t>
-  </si>
-  <si>
-    <t>走吧，克拉克还在等我们。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=41</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>浓稠的阴影在你眼角周围降下一圈暗沉的薄雾，仿佛还藏着什么尚未触及的秘密没有被发现。但现在，相较于分秒必争夺的营救，任何多余的停留都只会让克拉克的处境更加危险。</t>
-  </si>
-  <si>
-    <t>bgfade(sntzm_david313-315(5)_49,1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=42</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>大卫的脚步紧随其后，因神秘人的那句话而产生的犹疑并没有影响他当下的判断。两束手电很快为了同一个目标齐刷刷地照向一处，在楼梯口的黑暗中撕开一条明亮的通路。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=43; gotomainline=大卫线3层（上）_1</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>jump(51)</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>即将切断的通讯似乎因为这句话额外停留了片刻，仿佛一首曲子在临近结尾的时候突然混入了一丝令人不悦的杂音。</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>你是从哪里知道这个名字的？</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Un; 层级=28</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>有人告诉我，让我“不要相信亚波伦”。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=29</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>你将夜莺的原话抖了出来，但又在人称上进行了一些巧妙的修饰——用“我”而非“我们”，既部分透露了实情，又避免了对方对知情人身份最直接的怀疑。</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>神秘人的声线平稳了一些，又或者说因为这个意料之外的变量，开始逐渐认真起来。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=31</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>亚波伦</t>
+  </si>
+  <si>
+    <t>有人在帮你们。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Abaddon; 层级=32</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>他几乎坦然地评价道。</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>不过这对我而言也未必是件坏事，毕竟，如果我只是想要你们绝望地死在这里，我早就这么做了。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Abaddon; 层级=34</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>至于你们愿不愿意相信我，我想你们没有选择，现在时间还剩下大约13分钟，我想海尔特探员大概撑不到你们纠结犹豫的最后1分钟。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Abaddon; 层级=35</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>嘈杂的电磁声戛然而止，让病房中因承载太多过往而不堪重负的空气，再度回归冰冷的死寂。</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>你确定他可以相信吗？亚波伦这个名字在圣经里可是带来毁灭的魔鬼。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_David; 层级=39</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>八九不离十，但有一点他没说错，如果想解决我们他无需如此大费周折。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=40</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>你将手中的电筒重新射向走廊，削开一条明亮的光带，平稳中带着一丝焦急的抖动。直到将配枪的握把重新攥紧，这种情绪才稍微得到一些平息。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=41</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>我猜他大概是想利用我们达成某种目的，但这些也只有找到了克拉克，把他从暗处揪出来才能问得清楚。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_You; 层级=42</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>说完，你的脚已经擅自朝门边移了过去，没有任何多余的解释或预兆，只因解救同伴本身就是一种无需商量的责任。</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=43</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>51</t>
-  </si>
-  <si>
-    <t>即将切断的通讯似乎因为这句话额外停留了片刻，仿佛一首曲子在临近结尾的时候突然混入了一丝令人不悦的杂音。</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>你是从哪里知道这个名字的？</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Un; 层级=28</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>有人告诉我，让我“不要相信亚波伦”。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=29</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>你将夜莺的原话抖了出来，但又在人称上进行了一些巧妙的修饰——用“我”而非“我们”，既部分透露了实情，又避免了对方对知情人身份最直接的怀疑。</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>神秘人的声线平稳了一些，又或者说因为这个意料之外的变量，开始逐渐认真起来。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=31</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>亚波伦</t>
-  </si>
-  <si>
-    <t>有人在帮你们。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Abaddon; 层级=32</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>他几乎坦然地评价道。</t>
-  </si>
-  <si>
-    <t>58</t>
-  </si>
-  <si>
-    <t>不过这对我而言也未必是件坏事，毕竟，如果我只是想要你们绝望地死在这里，我早就这么做了。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Abaddon; 层级=34</t>
-  </si>
-  <si>
-    <t>59</t>
-  </si>
-  <si>
-    <t>至于你们愿不愿意相信我，我想你们没有选择，现在时间还剩下大约13分钟，我想海尔特探员大概撑不到你们纠结犹豫的最后1分钟。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Abaddon; 层级=35</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>嘈杂的电磁声戛然而止，让病房中因承载太多过往而不堪重负的空气，再度回归冰冷的死寂。</t>
-  </si>
-  <si>
-    <t>61</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>你确定他可以相信吗？亚波伦这个名字在圣经里可是带来毁灭的魔鬼。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_David; 层级=39</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>八九不离十，但有一点他没说错，如果想解决我们他无需如此大费周折。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=40</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>你将手中的电筒重新射向走廊，削开一条明亮的光带，平稳中带着一丝焦急的抖动。直到将配枪的握把重新攥紧，这种情绪才稍微得到一些平息。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=41</t>
-  </si>
-  <si>
-    <t>66</t>
-  </si>
-  <si>
-    <t>我猜他大概是想利用我们达成某种目的，但这些也只有找到了克拉克，把他从暗处揪出来才能问得清楚。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_You; 层级=42</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>说完，你的脚已经擅自朝门边移了过去，没有任何多余的解释或预兆，只因解救同伴本身就是一种无需商量的责任。</t>
-  </si>
-  <si>
     <t>68</t>
   </si>
   <si>
+    <t>他咬了咬牙，重新将手电的光柱对准了你劈开的光路，显然还没能完全放下对这场鸿门宴潜在的顾虑。</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=44</t>
   </si>
   <si>
     <t>69</t>
   </si>
   <si>
-    <t>不止是因为你们别无选择，关于自己身为记者的过去，他还有很多问题要向那个躲在暗处的男人逼问个明白。</t>
+    <t>夜莺的那句弥留之际的警告依旧如幽灵般环绕在他耳边，让他很难忽视这份邀请背后所有不利的可能。</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=45</t>
   </si>
   <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>但为了拯救克拉克的性命，以及在你这个愣头青被啃害时及时拉你一把。纵使前方危机四伏，眼下的你们也只有顶着被人算计的风险，偏向虎山行。</t>
+  </si>
+  <si>
+    <t>loadScript(sntzm_david3F(1), 1)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=46; gotomainline=大卫线3层（上）_1</t>
+  </si>
+  <si>
     <t>项目</t>
   </si>
   <si>
@@ -701,21 +720,21 @@
     <t>转换时间</t>
   </si>
   <si>
-    <t>2026/7/22 14:04:56</t>
+    <t>2026/9/24 16:46:54</t>
   </si>
   <si>
     <t>输出节点数</t>
   </si>
   <si>
-    <t>78</t>
-  </si>
-  <si>
     <t>选项节点数</t>
   </si>
   <si>
     <t>跳转行数</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>跨文件跳转数</t>
   </si>
   <si>
@@ -731,16 +750,16 @@
     <t>datatype=type:txt_* -&gt; 按 节点类型转中文.xlsx 的 Type/Name 映射生成 Speaker</t>
   </si>
   <si>
-    <t>selectBC 子节点 -&gt; Command 中的 choice(文本|jump(分支首句ID))</t>
+    <t>selectBC 子节点 -&gt; Command 中的 choice(文本|jump(选项入口ID))</t>
   </si>
   <si>
     <t>selectBC 直接子节点作为选项入口时，不再把选项文字写入 Text</t>
   </si>
   <si>
-    <t>选项入口 Note 除源类型/层级外，其余字段追加到分支首句 Note</t>
-  </si>
-  <si>
-    <t>gotomainline 数字 -&gt; jump(ID)；非数字 -&gt; loadScript(文件名, 1)</t>
+    <t>选项入口保留自身 tag 等 Note 字段；Command 优先使用 gotomainline，否则 jump 到第一个子节点</t>
+  </si>
+  <si>
+    <t>gotomainline 数字 -&gt; jump(ID)；文件名_数字 -&gt; loadScript(文件名, 数字)；其他非数字 -&gt; loadScript(文件名, 1)</t>
   </si>
   <si>
     <t>pic -&gt; Background；music -&gt; BGM；无语音时第一行 Voice=false</t>
@@ -1263,11 +1282,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1420,6 +1434,11 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -1728,28 +1747,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1758,118 +1780,115 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1880,7 +1899,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2208,7 +2227,7 @@
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
@@ -2243,7 +2262,7 @@
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
         <a:font script="Ethi" typeface="Nyala"/>
@@ -2416,7 +2435,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2505,7 +2524,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" ht="27" spans="1:12">
+    <row r="3" ht="30" spans="1:12">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -2539,7 +2558,7 @@
       <c r="K3" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -3525,15 +3544,15 @@
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="L29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" ht="40.5" spans="1:12">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3551,7 +3570,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3566,15 +3585,15 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
@@ -3589,7 +3608,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3604,15 +3623,15 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" ht="27" spans="1:12">
       <c r="A32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -3627,7 +3646,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -3642,12 +3661,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" ht="40.5" spans="1:12">
       <c r="A33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -3665,7 +3684,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3680,12 +3699,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" ht="30" spans="1:12">
       <c r="A34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B34" t="s">
         <v>54</v>
@@ -3703,7 +3722,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3718,12 +3737,12 @@
         <v>57</v>
       </c>
       <c r="L34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" ht="40.5" spans="1:12">
       <c r="A35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B35" t="s">
         <v>23</v>
@@ -3741,7 +3760,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -3756,15 +3775,15 @@
         <v>61</v>
       </c>
       <c r="L35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" ht="27" spans="1:12">
       <c r="A36" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
@@ -3779,7 +3798,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -3794,12 +3813,12 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B37" t="s">
         <v>54</v>
@@ -3817,7 +3836,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -3832,12 +3851,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" ht="40.5" spans="1:12">
       <c r="A38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -3855,7 +3874,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -3870,15 +3889,15 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" ht="43.5" spans="1:12">
       <c r="A39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
@@ -3893,7 +3912,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -3908,12 +3927,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" ht="40.5" spans="1:12">
       <c r="A40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -3931,7 +3950,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -3946,12 +3965,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" ht="57" spans="1:12">
       <c r="A41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -3969,7 +3988,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -3984,12 +4003,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" ht="27" spans="1:12">
       <c r="A42" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4007,7 +4026,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4022,12 +4041,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="43" ht="40.5" spans="1:12">
       <c r="A43" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4045,7 +4064,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4060,12 +4079,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B44" t="s">
         <v>31</v>
@@ -4083,7 +4102,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4098,12 +4117,12 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="45" ht="54" spans="1:12">
       <c r="A45" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4121,7 +4140,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4133,15 +4152,15 @@
         <v>15</v>
       </c>
       <c r="K45" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L45" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="46" ht="54" spans="1:12">
       <c r="A46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4159,7 +4178,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4170,16 +4189,16 @@
       <c r="J46" t="s">
         <v>15</v>
       </c>
-      <c r="K46" t="s">
-        <v>15</v>
+      <c r="K46" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="L46" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B47" t="s">
         <v>31</v>
@@ -4209,15 +4228,15 @@
         <v>15</v>
       </c>
       <c r="K47" t="s">
-        <v>15</v>
+        <v>162</v>
       </c>
       <c r="L47" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" ht="40.5" spans="1:12">
       <c r="A48" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4235,7 +4254,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4250,12 +4269,12 @@
         <v>15</v>
       </c>
       <c r="L48" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B49" t="s">
         <v>23</v>
@@ -4273,7 +4292,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4288,12 +4307,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B50" t="s">
         <v>31</v>
@@ -4311,7 +4330,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4326,12 +4345,12 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" ht="55.5" spans="1:12">
       <c r="A51" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4349,7 +4368,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4364,12 +4383,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" ht="27" spans="1:12">
       <c r="A52" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4387,7 +4406,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4402,15 +4421,15 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B53" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
@@ -4425,7 +4444,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4440,12 +4459,12 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4463,7 +4482,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4478,15 +4497,15 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" ht="27" spans="1:12">
       <c r="A55" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B55" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
@@ -4501,7 +4520,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4516,15 +4535,15 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="56" ht="43.5" spans="1:12">
       <c r="A56" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B56" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
@@ -4539,7 +4558,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4554,12 +4573,12 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="57" ht="27" spans="1:12">
       <c r="A57" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4577,7 +4596,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4592,12 +4611,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58" ht="57" spans="1:12">
       <c r="A58" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4615,7 +4634,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4630,12 +4649,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" ht="27" spans="1:12">
       <c r="A59" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4653,7 +4672,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4668,12 +4687,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60" ht="27" spans="1:12">
       <c r="A60" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B60" t="s">
         <v>54</v>
@@ -4691,7 +4710,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4706,12 +4725,12 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="61" ht="27" spans="1:12">
       <c r="A61" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B61" t="s">
         <v>31</v>
@@ -4729,7 +4748,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4744,12 +4763,12 @@
         <v>15</v>
       </c>
       <c r="L61" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="62" ht="40.5" spans="1:12">
       <c r="A62" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -4767,7 +4786,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -4779,15 +4798,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L62" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="63" ht="40.5" spans="1:12">
       <c r="A63" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B63" t="s">
         <v>31</v>
@@ -4805,7 +4824,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -4820,12 +4839,12 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="64" ht="40.5" spans="1:12">
       <c r="A64" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -4843,7 +4862,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -4858,12 +4877,12 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="65" ht="40.5" spans="1:12">
       <c r="A65" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -4881,7 +4900,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>15</v>
+        <v>208</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -4896,12 +4915,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="66" ht="40.5" spans="1:12">
       <c r="A66" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -4919,7 +4938,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -4934,7 +4953,45 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>207</v>
+        <v>212</v>
+      </c>
+    </row>
+    <row r="67" ht="40.5" spans="1:12">
+      <c r="A67" t="s">
+        <v>213</v>
+      </c>
+      <c r="B67" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" t="s">
+        <v>15</v>
+      </c>
+      <c r="E67" t="s">
+        <v>15</v>
+      </c>
+      <c r="F67" t="s">
+        <v>15</v>
+      </c>
+      <c r="G67" t="s">
+        <v>214</v>
+      </c>
+      <c r="H67" t="s">
+        <v>15</v>
+      </c>
+      <c r="I67" t="s">
+        <v>15</v>
+      </c>
+      <c r="J67" t="s">
+        <v>15</v>
+      </c>
+      <c r="K67" t="s">
+        <v>215</v>
+      </c>
+      <c r="L67" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -4955,63 +5012,63 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B2" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B3" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B4" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B8" t="s">
         <v>99</v>
@@ -5019,58 +5076,58 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B10" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B11" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B12" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="13" ht="58.5" spans="1:2">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="13" ht="88.5" spans="1:2">
       <c r="A13" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B13" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="14" ht="60" spans="1:2">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="14" ht="105" spans="1:2">
       <c r="A14" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B14" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B15" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -5092,616 +5149,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C2" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D2" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="E2" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="F2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B3" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C3" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="D3" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="E3" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="F3" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B4" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C4" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="D4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="E4" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="F4" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B5" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C5" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="E5" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="F5" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B6" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="C6" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="D6" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="E6" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="F6" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B7" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="C7" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="D7" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="E7" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="F7" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B8" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="C8" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="D8" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="E8" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="F8" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B9" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="C9" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="D9" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="E9" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="F9" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B10" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="C10" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="D10" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="E10" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="F10" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B11" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="C11" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="D11" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="E11" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F11" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B12" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="C12" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="D12" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="E12" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="F12" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B13" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C13" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="D13" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="E13" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="F13" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B14" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C14" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D14" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="E14" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="F14" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B15" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C15" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="D15" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="E15" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="F15" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B16" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="C16" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D16" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="E16" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="F16" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B17" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C17" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="D17" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="E17" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="F17" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B18" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C18" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="D18" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="E18" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="F18" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B19" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="C19" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="D19" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="E19" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="F19" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B20" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="C20" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="D20" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="E20" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="F20" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B21" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="C21" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="D21" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="E21" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="F21" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B22" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C22" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="D22" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="E22" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="F22" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B23" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C23" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="D23" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="E23" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="F23" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B24" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C24" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="D24" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="E24" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="F24" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B25" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="C25" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="D25" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="E25" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="F25" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B26" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="C26" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="D26" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="E26" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="F26" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B27" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="C27" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="D27" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="E27" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="F27" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B28" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="C28" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="D28" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="E28" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="F28" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B29" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="C29" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="D29" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="E29" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="F29" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="B30" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="C30" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="D30" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="E30" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="F30" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B31" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="C31" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="D31" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
